--- a/Auswertung/Portfolio_Profi_Analyse_B - Kydan.xlsx
+++ b/Auswertung/Portfolio_Profi_Analyse_B - Kydan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Portfolio_Excel\Auswertung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B39FEA3-F4E9-423F-BE71-9BC08B626117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C990F75B-FCA5-4EDE-BD8F-B93FF21908B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daten" sheetId="1" r:id="rId1"/>
